--- a/Team-Data/2013-14/2-1-2013-14.xlsx
+++ b/Team-Data/2013-14/2-1-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.543</v>
+        <v>0.533</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J2" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K2" t="n">
         <v>0.462</v>
@@ -694,70 +761,70 @@
         <v>0.372</v>
       </c>
       <c r="O2" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="R2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.1</v>
+        <v>102.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
         <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -766,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>6</v>
@@ -781,7 +848,7 @@
         <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
         <v>17</v>
@@ -793,22 +860,22 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -954,10 +1021,10 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -972,22 +1039,22 @@
         <v>17</v>
       </c>
       <c r="AU3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>28</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J4" t="n">
         <v>78.3</v>
@@ -1052,10 +1119,10 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -1064,25 +1131,25 @@
         <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.767</v>
+        <v>0.764</v>
       </c>
       <c r="R4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="X4" t="n">
         <v>4.1</v>
@@ -1091,7 +1158,7 @@
         <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
@@ -1100,10 +1167,10 @@
         <v>97.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1127,13 +1194,13 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1142,34 +1209,34 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS4" t="n">
         <v>26</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
         <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.429</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1231,10 +1298,10 @@
         <v>0.434</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
         <v>0.347</v>
@@ -1243,25 +1310,25 @@
         <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
         <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
         <v>20.4</v>
       </c>
       <c r="V5" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1282,7 +1349,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
         <v>2</v>
@@ -1291,10 +1358,10 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>14</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
         <v>10</v>
@@ -1324,10 +1391,10 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>9</v>
@@ -1339,7 +1406,7 @@
         <v>22</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>29</v>
@@ -1348,7 +1415,7 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1360,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -1389,82 +1456,82 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
         <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H6" t="n">
         <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.425</v>
+        <v>0.426</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.339</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.768</v>
+        <v>0.771</v>
       </c>
       <c r="R6" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U6" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
         <v>15.6</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
         <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="AD6" t="n">
         <v>21</v>
@@ -1491,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1500,31 +1567,31 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>0.348</v>
       </c>
       <c r="H7" t="n">
         <v>48.9</v>
@@ -1598,31 +1665,31 @@
         <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O7" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P7" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="U7" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V7" t="n">
         <v>14.7</v>
@@ -1637,19 +1704,19 @@
         <v>6.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AB7" t="n">
         <v>95.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1676,16 +1743,16 @@
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN7" t="n">
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
@@ -1694,13 +1761,13 @@
         <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1709,19 +1776,19 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY7" t="n">
         <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1840,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
@@ -1855,19 +1922,19 @@
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT8" t="n">
         <v>28</v>
@@ -1888,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2080,22 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2037,7 +2104,7 @@
         <v>14</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2046,16 +2113,16 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
         <v>5</v>
@@ -2064,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
@@ -2076,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
         <v>29</v>
@@ -2088,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.447</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M10" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.306</v>
+        <v>0.307</v>
       </c>
       <c r="O10" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.663</v>
+        <v>0.665</v>
       </c>
       <c r="R10" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>45</v>
+        <v>44.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
         <v>15.4</v>
@@ -2177,34 +2244,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z10" t="n">
         <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2219,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
         <v>24</v>
       </c>
-      <c r="AT10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>23</v>
-      </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2258,19 +2325,19 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2401,7 +2468,7 @@
         <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2443,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2452,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.653</v>
+        <v>0.646</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K12" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L12" t="n">
         <v>9</v>
@@ -2511,13 +2578,13 @@
         <v>26.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P12" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0.6860000000000001</v>
@@ -2541,22 +2608,22 @@
         <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2625,7 +2692,7 @@
         <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>0.783</v>
+        <v>0.778</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.779</v>
+        <v>0.776</v>
       </c>
       <c r="R13" t="n">
         <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="T13" t="n">
         <v>45.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>7.1</v>
@@ -2726,19 +2793,19 @@
         <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>21</v>
@@ -2750,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -2762,22 +2829,22 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
       </c>
       <c r="AM13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -2795,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2807,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.68</v>
+        <v>0.673</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,37 +2930,37 @@
         <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="R14" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
         <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
@@ -2914,13 +2981,13 @@
         <v>21.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2938,7 +3005,7 @@
         <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,13 +3014,13 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
         <v>22</v>
@@ -2971,7 +3038,7 @@
         <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>19</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3105,28 +3172,28 @@
         <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3144,7 +3211,7 @@
         <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
@@ -3156,7 +3223,7 @@
         <v>20</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV15" t="n">
         <v>18</v>
@@ -3165,16 +3232,16 @@
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,52 +3294,52 @@
         <v>37.7</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
         <v>15.4</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0.747</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S16" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X16" t="n">
         <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
         <v>19.6</v>
@@ -3281,10 +3348,10 @@
         <v>19</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AD16" t="n">
         <v>21</v>
@@ -3296,7 +3363,7 @@
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
@@ -3305,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
@@ -3317,10 +3384,10 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>27</v>
@@ -3329,13 +3396,13 @@
         <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>16</v>
@@ -3356,13 +3423,13 @@
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3391,19 +3458,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
         <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.717</v>
+        <v>0.711</v>
       </c>
       <c r="H17" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I17" t="n">
         <v>39.1</v>
@@ -3412,7 +3479,7 @@
         <v>76.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.51</v>
+        <v>0.509</v>
       </c>
       <c r="L17" t="n">
         <v>8</v>
@@ -3424,31 +3491,31 @@
         <v>0.37</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
         <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
         <v>7.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T17" t="n">
         <v>36.8</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
         <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X17" t="n">
         <v>4.4</v>
@@ -3466,7 +3533,7 @@
         <v>104.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD17" t="n">
         <v>21</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,13 +3587,13 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX17" t="n">
         <v>22</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.17</v>
+        <v>0.174</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
@@ -3603,16 +3670,16 @@
         <v>20.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R18" t="n">
         <v>11.4</v>
@@ -3621,10 +3688,10 @@
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="n">
         <v>15.6</v>
@@ -3633,7 +3700,7 @@
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
@@ -3651,7 +3718,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,16 +3748,16 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -3705,10 +3772,10 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
         <v>6</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J19" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="P19" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R19" t="n">
         <v>13</v>
@@ -3818,31 +3885,31 @@
         <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>22</v>
@@ -3851,7 +3918,7 @@
         <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3875,16 +3942,16 @@
         <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
         <v>6</v>
@@ -3905,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
         <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>0.435</v>
+        <v>0.422</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3961,19 +4028,19 @@
         <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O20" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.768</v>
@@ -3982,64 +4049,64 @@
         <v>12.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X20" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA20" t="n">
         <v>20.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH20" t="n">
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4048,25 +4115,25 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP20" t="n">
         <v>15</v>
       </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4087,10 +4154,10 @@
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.404</v>
+        <v>0.413</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4137,49 +4204,49 @@
         <v>36.6</v>
       </c>
       <c r="J21" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O21" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P21" t="n">
         <v>19.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W21" t="n">
         <v>7.8</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
         <v>3.7</v>
@@ -4191,22 +4258,22 @@
         <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG21" t="n">
         <v>21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>12</v>
@@ -4215,10 +4282,10 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,16 +4294,16 @@
         <v>7</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,10 +4315,10 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
         <v>13</v>
@@ -4263,7 +4330,7 @@
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4272,7 +4339,7 @@
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -4301,46 +4368,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
         <v>38</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.776</v>
+        <v>0.792</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J22" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.805</v>
+        <v>0.804</v>
       </c>
       <c r="R22" t="n">
         <v>11.2</v>
@@ -4355,13 +4422,13 @@
         <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
         <v>3.8</v>
@@ -4373,10 +4440,10 @@
         <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.4</v>
+        <v>105.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
         <v>2</v>
@@ -4385,10 +4452,10 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
         <v>25</v>
@@ -4397,7 +4464,7 @@
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4430,13 +4497,13 @@
         <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,13 +4512,13 @@
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,16 +4640,16 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>19</v>
@@ -4600,10 +4667,10 @@
         <v>20</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
@@ -4618,16 +4685,16 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313</v>
+        <v>0.319</v>
       </c>
       <c r="H24" t="n">
         <v>48.7</v>
@@ -4683,19 +4750,19 @@
         <v>38.8</v>
       </c>
       <c r="J24" t="n">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
         <v>21.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="O24" t="n">
         <v>16.7</v>
@@ -4704,19 +4771,19 @@
         <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.712</v>
+        <v>0.714</v>
       </c>
       <c r="R24" t="n">
         <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T24" t="n">
         <v>44.7</v>
       </c>
       <c r="U24" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V24" t="n">
         <v>17.2</v>
@@ -4728,22 +4795,22 @@
         <v>4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA24" t="n">
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>26</v>
@@ -4755,13 +4822,13 @@
         <v>27</v>
       </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -4779,28 +4846,28 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS24" t="n">
         <v>10</v>
       </c>
-      <c r="AS24" t="n">
-        <v>11</v>
-      </c>
       <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
         <v>10</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
         <v>24</v>
@@ -4809,7 +4876,7 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,7 +4932,7 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K25" t="n">
         <v>0.458</v>
@@ -4880,55 +4947,55 @@
         <v>0.371</v>
       </c>
       <c r="O25" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
         <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="V25" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
         <v>21.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
         <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4949,31 +5016,31 @@
         <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
@@ -4994,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
         <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>0.723</v>
+        <v>0.717</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="J26" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="K26" t="n">
         <v>0.453</v>
@@ -5056,31 +5123,31 @@
         <v>9.6</v>
       </c>
       <c r="M26" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.821</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T26" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5089,25 +5156,25 @@
         <v>5.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>108.3</v>
+        <v>108.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5125,7 +5192,7 @@
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>13</v>
@@ -5134,16 +5201,16 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5176,7 +5243,7 @@
         <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5211,34 +5278,34 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J27" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
         <v>0.345</v>
@@ -5253,19 +5320,19 @@
         <v>0.772</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T27" t="n">
         <v>43.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
         <v>7.4</v>
@@ -5274,28 +5341,28 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC27" t="n">
         <v>-2.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
@@ -5328,13 +5395,13 @@
         <v>6</v>
       </c>
       <c r="AQ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR27" t="n">
         <v>7</v>
       </c>
-      <c r="AR27" t="n">
-        <v>9</v>
-      </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5343,7 +5410,7 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5393,64 +5460,64 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.723</v>
+        <v>0.717</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.492</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="O28" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P28" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U28" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.8</v>
@@ -5459,19 +5526,19 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.8</v>
+        <v>104</v>
       </c>
       <c r="AC28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5510,10 +5577,10 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5531,7 +5598,7 @@
         <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5540,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5575,37 +5642,37 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>0.532</v>
+        <v>0.543</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.438</v>
       </c>
       <c r="L29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M29" t="n">
         <v>22.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
         <v>18.8</v>
@@ -5614,55 +5681,55 @@
         <v>24.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R29" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S29" t="n">
         <v>31.6</v>
       </c>
       <c r="T29" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V29" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA29" t="n">
         <v>21.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG29" t="n">
         <v>12</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
@@ -5683,34 +5750,34 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
       </c>
       <c r="AQ29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR29" t="n">
         <v>8</v>
       </c>
-      <c r="AR29" t="n">
-        <v>11</v>
-      </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>21</v>
@@ -5719,7 +5786,7 @@
         <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5757,49 +5824,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>0.34</v>
+        <v>0.348</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O30" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R30" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
         <v>30.6</v>
@@ -5808,7 +5875,7 @@
         <v>41.6</v>
       </c>
       <c r="U30" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5823,19 +5890,19 @@
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5871,13 +5938,13 @@
         <v>22</v>
       </c>
       <c r="AP30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>19</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>20</v>
-      </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5889,13 +5956,13 @@
         <v>26</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F31" t="n">
         <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J31" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.449</v>
@@ -5969,16 +6036,16 @@
         <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
@@ -5990,19 +6057,19 @@
         <v>43</v>
       </c>
       <c r="U31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z31" t="n">
         <v>20.6</v>
@@ -6011,22 +6078,22 @@
         <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
@@ -6035,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>17</v>
@@ -6050,34 +6117,34 @@
         <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-1-2013-14</t>
+          <t>2014-02-01</t>
         </is>
       </c>
     </row>
